--- a/data/evaluation_results_10.xlsx
+++ b/data/evaluation_results_10.xlsx
@@ -13,9 +13,9 @@
     <sheet name="Metadata" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Runs'!$A$1:$K$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Runs'!$A$1:$J$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Prompts'!$A$1:$B$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Scores'!$A$1:$B$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Scores'!$A$1:$B$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Metadata'!$A$1:$B$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -439,11 +439,10 @@
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -479,25 +478,20 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>ttft_seconds</t>
+          <t>total_latency_seconds</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>total_latency_seconds</t>
+          <t>input_tokens</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>input_tokens</t>
+          <t>output_tokens</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>output_tokens</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>error</t>
         </is>
@@ -523,31 +517,31 @@
       <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Based on the information provided, the most likely consequence for the student who is caught wearing a non-uniform would be:
-1. Detention or time-out: The student would likely receive a detention or be sent to a time-out area as a consequence for not following the school's uniform policy.
-2. Verbal warning or reminder: The student may also receive a verbal warning or reminder from a teacher or school administrator about the importance of wearing the uniform.
-3. Parent contact: Depending on the school's policies, the student's parents or guardians may be contacted and informed about the infraction, and they may be asked to speak with the student about the importance of following the uniform policy.
-It's unlikely that the student would face more severe consequences, such as suspension or expulsion, unless the infraction is part of a larger pattern of non-compliance with school rules or policies.
-Other possible consequences, such as loss of privileges or extra work, may also be considered, but detention, verbal warning, and parent contact are the most likely outcomes.</t>
+1. Detention or time-out
+This is a common consequence for students who break school rules, including wearing non-uniform attire. The exact consequence may vary depending on the school's policies and the student's behavior, but detention or time-out is a likely outcome.
+Other possible consequences could include:
+* Verbal warning or reminder
+* Parent contact or notification
+* Loss of privileges (e.g., extracurricular activities)
+* Detention or suspension (in more severe cases)
+However, detention or time-out is the most likely and common consequence for a student caught wearing a non-uniform.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:05:31.124255+00:00</t>
+          <t>2026-10-22T04:48:24.054351+00:00</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1.991720493000003</v>
+        <v>1.409886174000007</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>2.020022184000027</v>
+        <v>75</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>210</v>
-      </c>
-      <c r="K2" s="2" t="inlineStr"/>
+        <v>146</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -571,34 +565,26 @@
           <t>Based on the information provided, the most likely consequence for the student who is caught wearing a non-uniform would be:
 1. Detention or time-out: The student would likely receive a detention or time-out as a consequence for not following the school's uniform policy.
 2. Verbal warning or reminder: The student may also receive a verbal warning or reminder from the teacher or school administrator about the importance of wearing the uniform.
-3. Parent contact: Depending on the school's policies, the student's parent or guardian may be contacted to discuss the incident and the consequences.
-It's unlikely that the student would face more severe consequences, such as suspension or expulsion, unless the school has a specific policy in place for repeated offenses or serious infractions.
-Other possible consequences that are less likely include:
-* Loss of privileges (e.g., recess, extracurricular activities)
-* Detention or suspension for a longer period
-* Parent-teacher conference
-* Loss of points or rewards
-However, these consequences would depend on the specific school's policies and the student's individual circumstances.</t>
+3. Parent contact: Depending on the school's policies, the student's parents or guardians may be contacted to discuss the incident and the consequences.
+4. Loss of privileges: The student may also face loss of privileges, such as participating in extracurricular activities or attending certain events.
+It's worth noting that the specific consequence would depend on the school's policies and the student's behavior. However, detention or time-out is a common consequence for students who fail to follow the uniform policy.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:05:33.144688+00:00</t>
+          <t>2026-10-22T04:48:25.464595+00:00</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>1.938059324999813</v>
+        <v>1.698643763999939</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>1.967015648999904</v>
+        <v>75</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>218</v>
-      </c>
-      <c r="K3" s="2" t="inlineStr"/>
+        <v>186</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -620,34 +606,30 @@
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Based on the information provided, the most likely consequence for the student who is caught wearing a non-uniform would be:
-Disciplinary action, such as detention, suspension, or a warning.
-This is because the school has a policy requiring students to wear a uniform, and the student has failed to comply with that policy. The consequence would likely be a consequence for breaking the rule, rather than a punishment for the student's personal choice or style.
-Other possible consequences might include:
-* A verbal warning or reprimand
-* A parent contact or meeting
-* A loss of privileges (e.g. extracurricular activities)
-* A temporary or permanent removal from class or school
-However, the most likely consequence would be disciplinary action, as it is a direct result of the student's failure to follow the school's uniform policy.</t>
+1. Detention or time-out
+This is a common consequence for students who break school rules, including wearing non-uniform attire. The school administration may also consider other consequences, such as:
+2. Verbal warning or reminder
+3. Parent contact or notification
+4. Loss of privileges (e.g., recess, extracurricular activities)
+5. Detention or suspension (in more severe cases)
+However, detention or time-out is a likely consequence, as it is a common disciplinary action used to teach students about the importance of following rules and respecting school policies.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:05:35.112133+00:00</t>
+          <t>2026-10-22T04:48:27.163676+00:00</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1.537221721999913</v>
+        <v>1.360502790000055</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1.56045114099993</v>
+        <v>75</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>168</v>
-      </c>
-      <c r="K4" s="2" t="inlineStr"/>
+        <v>141</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -685,22 +667,19 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:05:36.672947+00:00</t>
+          <t>2026-10-22T04:48:28.524514+00:00</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>1.645080473000007</v>
+        <v>1.741222376999985</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>1.663799227000027</v>
+        <v>72</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>72</v>
-      </c>
-      <c r="J5" s="2" t="n">
         <v>185</v>
       </c>
-      <c r="K5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -738,22 +717,19 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:05:38.336973+00:00</t>
+          <t>2026-10-22T04:48:30.265950+00:00</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1.655815935999954</v>
+        <v>1.623048329999961</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>1.674754552999957</v>
+        <v>72</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>72</v>
-      </c>
-      <c r="J6" s="2" t="n">
         <v>185</v>
       </c>
-      <c r="K6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -777,7 +753,7 @@
           <t>To solve this problem, let's consider the information given:
 1. The total cost of the bat and the ball together is $1.10.
 2. The bat costs $1.00 more than the ball.
-Let's denote the cost of the ball as x. Since the bat costs $1.00 more than the ball, the cost of the bat can be represented as x + $1.00.
+Let's denote the cost of the ball as x. Since the bat costs $1.00 more than the ball, the cost of the bat is x + $1.00.
 The total cost of the bat and the ball together is $1.10, so we can set up the equation:
 x + (x + $1.00) = $1.10
 Combine like terms:
@@ -791,22 +767,19 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:05:40.011955+00:00</t>
+          <t>2026-10-22T04:48:31.889220+00:00</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>1.665560891999803</v>
+        <v>1.601113792999968</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1.69657276099997</v>
+        <v>72</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>72</v>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>185</v>
-      </c>
-      <c r="K7" s="2" t="inlineStr"/>
+        <v>182</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -833,30 +806,27 @@
 Day 3: The snail climbs 3 feet, so it's at 5 feet. At night, it slips back 2 feet, so it's at 3 feet.
 Notice a pattern? The snail effectively climbs 1 foot per day (3 feet up, 2 feet back).
 Since the well is 20 feet deep, the snail needs to climb 19 feet (20 - 1 foot, since it starts at the bottom).
-To find the number of days, we can divide the total distance (19 feet) by the snail's daily progress (1 foot):
+To find the number of days, we can divide the total distance to climb (19 feet) by the effective daily progress (1 foot):
 19 feet / 1 foot/day = 19 days
-However, this calculation assumes the snail climbs 1 foot per day, but it actually climbs 3 feet up and slips back 2 feet, so it effectively climbs 1 foot per day. But, on the 19th day, the snail will climb 3 feet and reach the top of the well, so we need to add 1 more day to the total.
-Therefore, the snail will take 19 + 1 = 20 days to reach the top of the well.</t>
+However, this calculation assumes the snail climbs 3 feet on the final day and reaches the top. Since the snail climbs 3 feet on the 19th day, it will reach the top on the 20th day.
+Therefore, it will take the snail 20 days to reach the top of the well.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:05:41.708765+00:00</t>
+          <t>2026-10-22T04:48:33.490593+00:00</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>2.851701202999948</v>
+        <v>2.499045292000005</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>2.879615717999968</v>
+        <v>94</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>94</v>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>330</v>
-      </c>
-      <c r="K8" s="2" t="inlineStr"/>
+        <v>295</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -876,6 +846,53 @@
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>To solve this problem, let's analyze the snail's movement:
+- The snail climbs 3 feet up during the day.
+- At night, it slips back 2 feet.
+This means the snail effectively moves 1 foot up each day (3 feet up - 2 feet back = 1 foot net progress).
+Since the well is 20 feet deep, the snail needs to cover 19 feet (20 - 1 foot net progress).
+To find the number of days it will take for the snail to reach the top, we can divide the total distance by the net progress:
+19 feet (total distance) / 1 foot (net progress) = 19 days
+However, we need to consider that on the 19th day, the snail will climb 3 feet and reach the top of the well. So, the correct answer is 19 days.
+But, if we consider the snail's first day, it climbs 3 feet and slips back 2 feet, so it's still 1 foot away from the top. On the second day, it climbs 3 feet and slips back 2 feet, making it 2 feet away from the top. This pattern continues until the 19th day, when it reaches the top.
+Therefore, the snail will reach the top of the well on the 19th day.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T04:48:35.990008+00:00</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>2.374816736000071</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>281</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>A snail is at the bottom of a 20-foot well. Each day, it climbs up 3 feet, but at night, it slips back 2 feet. How many days will it take for the snail to reach the top of the well?</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>To solve this problem, let's analyze the snail's movement:
 Day 1: The snail climbs 3 feet, so it's at 3 feet. At night, it slips back 2 feet, so it's at 1 foot.
@@ -883,80 +900,29 @@
 Day 3: The snail climbs 3 feet, so it's at 5 feet. At night, it slips back 2 feet, so it's at 3 feet.
 Notice a pattern? The snail effectively climbs 1 foot per day (3 feet up, 2 feet back).
 Since the well is 20 feet deep, the snail needs to climb 19 feet (20 - 1 foot, since it starts at 1 foot).
-To climb 19 feet at a rate of 1 foot per day, the snail will need 19 days.
-However, on the 19th day, the snail will climb 3 feet and reach the top of the well. So, the correct answer is 19 days.</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21T18:05:44.588663+00:00</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>2.146609334999994</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>2.179634289999967</v>
-      </c>
-      <c r="I9" s="2" t="n">
+To climb 19 feet, the snail needs 19 days (1 foot per day).
+However, on the 19th day, the snail will climb 3 feet and reach the top of the well. So, the correct answer is 18 days (since it climbs 3 feet on the 19th day and reaches the top).
+Therefore, it will take the snail 18 days to reach the top of the well.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T04:48:38.365199+00:00</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>2.345323946000008</v>
+      </c>
+      <c r="H10" s="2" t="n">
         <v>94</v>
       </c>
-      <c r="J9" s="2" t="n">
-        <v>245</v>
-      </c>
-      <c r="K9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>A snail is at the bottom of a 20-foot well. Each day, it climbs up 3 feet, but at night, it slips back 2 feet. How many days will it take for the snail to reach the top of the well?</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>To solve this problem, let's analyze the snail's progress day by day.
-Day 1: The snail climbs 3 feet, so it's at 3 feet. At night, it slips back 2 feet, so it's at 1 foot.
-Day 2: The snail climbs 3 feet, so it's at 4 feet. At night, it slips back 2 feet, so it's at 2 feet.
-Day 3: The snail climbs 3 feet, so it's at 5 feet. At night, it slips back 2 feet, so it's at 3 feet.
-Notice a pattern? The snail effectively climbs 1 foot per day (3 feet up, 2 feet back).
-Since the well is 20 feet deep, the snail needs to climb 19 feet (20 - 1 foot, since it starts at the bottom).
-To climb 19 feet, the snail needs 19 days (1 foot per day).
-However, on the 19th day, the snail will climb 3 feet and reach the top of the well. So, it will take the snail 18 days to climb 18 feet, and then 1 more day to climb the final 3 feet.
-Therefore, the snail will reach the top of the well in 18 + 1 = 19 days.</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21T18:05:46.768529+00:00</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>2.482006461000083</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>2.517332357000214</v>
-      </c>
       <c r="I10" s="2" t="n">
-        <v>94</v>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>286</v>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
+        <v>276</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K10"/>
+  <autoFilter ref="A1:J10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1028,7 +994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1056,10 +1022,12 @@
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>{
-  "median_ttft": 1.6558159359999536,
-  "median_latency": 1.674754552999957,
-  "correct_frequency": 0.75,
-  "misinformation_frequency": 0
+  "median_input": 81,
+  "median_output": 283,
+  "median_latency": 2.399,
+  "correct_frequency": 0.8333333333333334,
+  "misinformation_frequency": 0,
+  "relevance_frequency": 1
 }</t>
         </is>
       </c>
@@ -1067,45 +1035,65 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>median_ttft</t>
+          <t>median_input</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1.655815935999954</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>median_latency</t>
+          <t>median_output</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.674754552999957</v>
+        <v>283</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>correct_frequency</t>
+          <t>median_latency</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.75</v>
+        <v>2.399</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>correct_frequency</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
           <t>misinformation_frequency</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B7" s="2" t="n">
         <v>0</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>relevance_frequency</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B6"/>
+  <autoFilter ref="A1:B8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1143,7 +1131,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:05:50.843922+00:00</t>
+          <t>2026-10-22T04:48:42.222944+00:00</t>
         </is>
       </c>
     </row>
